--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/196.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/196.xlsx
@@ -426,13 +426,13 @@
         <v>-11.68202526485131</v>
       </c>
       <c r="E2">
-        <v>-15.40186747977938</v>
+        <v>-15.8248360090438</v>
       </c>
       <c r="F2">
-        <v>3.958279870342844</v>
+        <v>1.361535877915653</v>
       </c>
       <c r="G2">
-        <v>-9.018840910211887</v>
+        <v>-10.80498285556041</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.41449008160142</v>
       </c>
       <c r="E3">
-        <v>-14.98011711002301</v>
+        <v>-15.38495362936073</v>
       </c>
       <c r="F3">
-        <v>3.871831699242666</v>
+        <v>1.831639974442868</v>
       </c>
       <c r="G3">
-        <v>-9.06905857549709</v>
+        <v>-7.730300443780137</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.08893344261783</v>
       </c>
       <c r="E4">
-        <v>-15.66307438901581</v>
+        <v>-17.26175703946967</v>
       </c>
       <c r="F4">
-        <v>4.126040254259429</v>
+        <v>1.919622756575106</v>
       </c>
       <c r="G4">
-        <v>-7.950915198517169</v>
+        <v>-9.165117364864583</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.71947609188384</v>
       </c>
       <c r="E5">
-        <v>-16.21334737958387</v>
+        <v>-18.43426952953568</v>
       </c>
       <c r="F5">
-        <v>4.418115217714349</v>
+        <v>1.878739388368037</v>
       </c>
       <c r="G5">
-        <v>-8.286068207821906</v>
+        <v>-9.219939998994915</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.3011950092482</v>
       </c>
       <c r="E6">
-        <v>-17.1930555602993</v>
+        <v>-17.46503570919998</v>
       </c>
       <c r="F6">
-        <v>4.242460059809298</v>
+        <v>1.791824024022804</v>
       </c>
       <c r="G6">
-        <v>-8.313883411442863</v>
+        <v>-9.337629892916006</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.839347713023743</v>
       </c>
       <c r="E7">
-        <v>-17.47175143615336</v>
+        <v>-16.71100855913081</v>
       </c>
       <c r="F7">
-        <v>4.390915068616676</v>
+        <v>1.755303765612771</v>
       </c>
       <c r="G7">
-        <v>-8.410392435003695</v>
+        <v>-7.553841745445904</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.339745722958311</v>
       </c>
       <c r="E8">
-        <v>-18.0502956899513</v>
+        <v>-20.65833444044882</v>
       </c>
       <c r="F8">
-        <v>4.213603354324076</v>
+        <v>2.655015014703498</v>
       </c>
       <c r="G8">
-        <v>-8.265231634197733</v>
+        <v>-8.693212340423633</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.816258302527038</v>
       </c>
       <c r="E9">
-        <v>-19.94036300042871</v>
+        <v>-19.49740125842042</v>
       </c>
       <c r="F9">
-        <v>4.091764107131572</v>
+        <v>2.210676229714568</v>
       </c>
       <c r="G9">
-        <v>-7.822763980691981</v>
+        <v>-7.920478042829109</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.283966208982488</v>
       </c>
       <c r="E10">
-        <v>-18.8700445832938</v>
+        <v>-21.26626849055654</v>
       </c>
       <c r="F10">
-        <v>4.697379584019279</v>
+        <v>2.3326928519696</v>
       </c>
       <c r="G10">
-        <v>-6.570685862829765</v>
+        <v>-5.744933178423813</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.759404052482047</v>
       </c>
       <c r="E11">
-        <v>-19.51112706313767</v>
+        <v>-20.17611082879402</v>
       </c>
       <c r="F11">
-        <v>4.855895876507445</v>
+        <v>2.991245282786785</v>
       </c>
       <c r="G11">
-        <v>-5.463301758852475</v>
+        <v>-5.901171064604178</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.259872600404002</v>
       </c>
       <c r="E12">
-        <v>-19.55502156169402</v>
+        <v>-21.98472900576947</v>
       </c>
       <c r="F12">
-        <v>4.827194374201936</v>
+        <v>2.888180869221817</v>
       </c>
       <c r="G12">
-        <v>-4.972635872840474</v>
+        <v>-6.539119811112814</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.799165338582057</v>
       </c>
       <c r="E13">
-        <v>-21.82005104848054</v>
+        <v>-21.84008048901646</v>
       </c>
       <c r="F13">
-        <v>4.651770437360539</v>
+        <v>2.455819652071355</v>
       </c>
       <c r="G13">
-        <v>-5.144459807419727</v>
+        <v>-6.415467624675496</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.398324532359382</v>
       </c>
       <c r="E14">
-        <v>-22.37535970214512</v>
+        <v>-22.9552806120414</v>
       </c>
       <c r="F14">
-        <v>5.082718988834428</v>
+        <v>3.137030163420733</v>
       </c>
       <c r="G14">
-        <v>-5.222956152701386</v>
+        <v>-5.056356258983103</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.071029817679975</v>
       </c>
       <c r="E15">
-        <v>-22.67481863132435</v>
+        <v>-25.69982115455212</v>
       </c>
       <c r="F15">
-        <v>5.603121585236</v>
+        <v>2.878471168254258</v>
       </c>
       <c r="G15">
-        <v>-4.190198366270347</v>
+        <v>-4.192416431781658</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.826431169838614</v>
       </c>
       <c r="E16">
-        <v>-25.47273176848947</v>
+        <v>-24.80648455858498</v>
       </c>
       <c r="F16">
-        <v>6.006062297595343</v>
+        <v>3.65347191132779</v>
       </c>
       <c r="G16">
-        <v>-4.037244541264939</v>
+        <v>-5.239522122579899</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.6676071605044</v>
       </c>
       <c r="E17">
-        <v>-24.24141251495985</v>
+        <v>-26.16107340307739</v>
       </c>
       <c r="F17">
-        <v>5.622696190350831</v>
+        <v>3.788528768090551</v>
       </c>
       <c r="G17">
-        <v>-3.239432861210437</v>
+        <v>-4.758158869533251</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.589928923662725</v>
       </c>
       <c r="E18">
-        <v>-24.54681280203714</v>
+        <v>-24.42908153478573</v>
       </c>
       <c r="F18">
-        <v>6.247230618104378</v>
+        <v>4.098553454391062</v>
       </c>
       <c r="G18">
-        <v>-3.19522052553347</v>
+        <v>-3.962614913173149</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.589242170530968</v>
       </c>
       <c r="E19">
-        <v>-26.94838483710294</v>
+        <v>-26.73556920111247</v>
       </c>
       <c r="F19">
-        <v>6.249701199332463</v>
+        <v>3.769183800333458</v>
       </c>
       <c r="G19">
-        <v>-2.787573190009773</v>
+        <v>-5.466132275288551</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.655753663856132</v>
       </c>
       <c r="E20">
-        <v>-27.0921231305804</v>
+        <v>-27.64631777963911</v>
       </c>
       <c r="F20">
-        <v>6.5149133430497</v>
+        <v>4.857322795537256</v>
       </c>
       <c r="G20">
-        <v>-1.925841496683022</v>
+        <v>-4.077500775022477</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.77962335213003</v>
       </c>
       <c r="E21">
-        <v>-27.83701634857611</v>
+        <v>-27.44970049517407</v>
       </c>
       <c r="F21">
-        <v>6.403501215604449</v>
+        <v>4.936185015302478</v>
       </c>
       <c r="G21">
-        <v>-1.730049212399446</v>
+        <v>-2.390519600211744</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.948374320002352</v>
       </c>
       <c r="E22">
-        <v>-28.097313034537</v>
+        <v>-28.56811583474445</v>
       </c>
       <c r="F22">
-        <v>6.361526674021643</v>
+        <v>4.695121219383863</v>
       </c>
       <c r="G22">
-        <v>-1.108931279412464</v>
+        <v>-3.846904725484543</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.148094819448201</v>
       </c>
       <c r="E23">
-        <v>-27.64792991638583</v>
+        <v>-26.58204940377844</v>
       </c>
       <c r="F23">
-        <v>6.670989144722173</v>
+        <v>5.062913162655943</v>
       </c>
       <c r="G23">
-        <v>-2.346889920549689</v>
+        <v>-3.081139126250185</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.366239242106173</v>
       </c>
       <c r="E24">
-        <v>-29.15089874021357</v>
+        <v>-30.14495312658531</v>
       </c>
       <c r="F24">
-        <v>6.975174707312457</v>
+        <v>4.572162292109144</v>
       </c>
       <c r="G24">
-        <v>-1.76091673900761</v>
+        <v>-1.768150281010918</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.589225583245446</v>
       </c>
       <c r="E25">
-        <v>-29.0265196731189</v>
+        <v>-30.69138597119486</v>
       </c>
       <c r="F25">
-        <v>6.881235607232251</v>
+        <v>5.256796775647701</v>
       </c>
       <c r="G25">
-        <v>-1.279457480140323</v>
+        <v>-5.018241948189473</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.808999969700672</v>
       </c>
       <c r="E26">
-        <v>-29.94548969620645</v>
+        <v>-31.6320745556232</v>
       </c>
       <c r="F26">
-        <v>6.882366373255875</v>
+        <v>5.182867799809073</v>
       </c>
       <c r="G26">
-        <v>-1.252999600190468</v>
+        <v>-2.39626008617684</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.016894708355437</v>
       </c>
       <c r="E27">
-        <v>-30.15626072618246</v>
+        <v>-30.20743248246913</v>
       </c>
       <c r="F27">
-        <v>6.932953107606842</v>
+        <v>4.768335943854629</v>
       </c>
       <c r="G27">
-        <v>-0.5721031464008662</v>
+        <v>-2.005463427448034</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.206128704455707</v>
       </c>
       <c r="E28">
-        <v>-31.32326432761814</v>
+        <v>-30.86424914525266</v>
       </c>
       <c r="F28">
-        <v>6.65737719237897</v>
+        <v>5.128885599975404</v>
       </c>
       <c r="G28">
-        <v>-1.280732040172943</v>
+        <v>-2.178608269697456</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.370195728118254</v>
       </c>
       <c r="E29">
-        <v>-30.72255092931564</v>
+        <v>-29.24264109513497</v>
       </c>
       <c r="F29">
-        <v>6.631293555951682</v>
+        <v>5.020219618587526</v>
       </c>
       <c r="G29">
-        <v>-1.655919476684085</v>
+        <v>-3.075468161741413</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.505710376465442</v>
       </c>
       <c r="E30">
-        <v>-29.99228694660172</v>
+        <v>-31.00770667334164</v>
       </c>
       <c r="F30">
-        <v>6.544797873674042</v>
+        <v>4.384779791900264</v>
       </c>
       <c r="G30">
-        <v>-1.263159664450491</v>
+        <v>-4.275693204822025</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.612290945974101</v>
       </c>
       <c r="E31">
-        <v>-29.74186686245156</v>
+        <v>-30.42789671105856</v>
       </c>
       <c r="F31">
-        <v>6.585616309938578</v>
+        <v>4.552161670103059</v>
       </c>
       <c r="G31">
-        <v>-1.072399409386607</v>
+        <v>-3.407297383324722</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.6905327871117</v>
       </c>
       <c r="E32">
-        <v>-29.79776181712823</v>
+        <v>-29.85980870374433</v>
       </c>
       <c r="F32">
-        <v>6.175643943314684</v>
+        <v>4.747163379471118</v>
       </c>
       <c r="G32">
-        <v>-2.298569197858487</v>
+        <v>-2.669416509167645</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.740836912845267</v>
       </c>
       <c r="E33">
-        <v>-29.35535028471188</v>
+        <v>-28.64177146447921</v>
       </c>
       <c r="F33">
-        <v>6.601575314448461</v>
+        <v>4.649907999203982</v>
       </c>
       <c r="G33">
-        <v>-1.164065104823486</v>
+        <v>-4.215143326908755</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.761677865724865</v>
       </c>
       <c r="E34">
-        <v>-30.30044960282369</v>
+        <v>-27.96354191235042</v>
       </c>
       <c r="F34">
-        <v>7.159842735582274</v>
+        <v>4.623895629542889</v>
       </c>
       <c r="G34">
-        <v>-1.313936811931832</v>
+        <v>-4.208456024919427</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.753998922870782</v>
       </c>
       <c r="E35">
-        <v>-29.55613829373797</v>
+        <v>-30.28174474093501</v>
       </c>
       <c r="F35">
-        <v>6.878205977816016</v>
+        <v>5.17691306556702</v>
       </c>
       <c r="G35">
-        <v>-1.192767534648968</v>
+        <v>-3.351137288796525</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.717177941886244</v>
       </c>
       <c r="E36">
-        <v>-28.62895135456349</v>
+        <v>-29.97867661797167</v>
       </c>
       <c r="F36">
-        <v>6.624710090461201</v>
+        <v>4.977017704920254</v>
       </c>
       <c r="G36">
-        <v>-1.965015182049218</v>
+        <v>-3.106382035987127</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.652179804656199</v>
       </c>
       <c r="E37">
-        <v>-27.07332543497457</v>
+        <v>-26.58965724011133</v>
       </c>
       <c r="F37">
-        <v>6.939943585517592</v>
+        <v>4.462902421002976</v>
       </c>
       <c r="G37">
-        <v>-2.320504872601698</v>
+        <v>-3.237843799351587</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.558261542312059</v>
       </c>
       <c r="E38">
-        <v>-27.10862036139035</v>
+        <v>-29.12073457484848</v>
       </c>
       <c r="F38">
-        <v>6.613206050691448</v>
+        <v>4.820257742292311</v>
       </c>
       <c r="G38">
-        <v>-2.216871555040352</v>
+        <v>-2.751193605078722</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.433879003356993</v>
       </c>
       <c r="E39">
-        <v>-25.66664555397192</v>
+        <v>-27.2143285301514</v>
       </c>
       <c r="F39">
-        <v>6.873255313124353</v>
+        <v>5.120929061456236</v>
       </c>
       <c r="G39">
-        <v>-1.733204162298371</v>
+        <v>-3.132240707194375</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.279734915463908</v>
       </c>
       <c r="E40">
-        <v>-25.72638518308111</v>
+        <v>-26.56934703418692</v>
       </c>
       <c r="F40">
-        <v>6.570053231907554</v>
+        <v>5.475207242151871</v>
       </c>
       <c r="G40">
-        <v>-2.310414329797999</v>
+        <v>-2.35142867848403</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.097738147348047</v>
       </c>
       <c r="E41">
-        <v>-26.16811518015932</v>
+        <v>-25.92149901417559</v>
       </c>
       <c r="F41">
-        <v>7.173820523991943</v>
+        <v>4.896486259120158</v>
       </c>
       <c r="G41">
-        <v>-3.35311368448347</v>
+        <v>-4.811210361800072</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.893077480780724</v>
       </c>
       <c r="E42">
-        <v>-26.54490233149352</v>
+        <v>-23.74667220114786</v>
       </c>
       <c r="F42">
-        <v>6.996285507165266</v>
+        <v>4.697157865191118</v>
       </c>
       <c r="G42">
-        <v>-2.283592289838824</v>
+        <v>-3.530204697015703</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.670618812238001</v>
       </c>
       <c r="E43">
-        <v>-24.64558787709245</v>
+        <v>-24.28148045297972</v>
       </c>
       <c r="F43">
-        <v>7.549450227839533</v>
+        <v>5.552441412236022</v>
       </c>
       <c r="G43">
-        <v>-3.046802147916864</v>
+        <v>-2.463245664618453</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.436490353485372</v>
       </c>
       <c r="E44">
-        <v>-22.69423672786924</v>
+        <v>-22.64082337694877</v>
       </c>
       <c r="F44">
-        <v>7.13160842652182</v>
+        <v>4.428003877450353</v>
       </c>
       <c r="G44">
-        <v>-2.618023600215999</v>
+        <v>-4.763571611489959</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.196306249550417</v>
       </c>
       <c r="E45">
-        <v>-22.52746208711475</v>
+        <v>-22.91125931621283</v>
       </c>
       <c r="F45">
-        <v>7.72568343840372</v>
+        <v>4.633929990223113</v>
       </c>
       <c r="G45">
-        <v>-3.462818542563839</v>
+        <v>-3.644888615587136</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.959902072417925</v>
       </c>
       <c r="E46">
-        <v>-20.85476152900552</v>
+        <v>-19.70569294887722</v>
       </c>
       <c r="F46">
-        <v>7.308760186516961</v>
+        <v>5.074184397656126</v>
       </c>
       <c r="G46">
-        <v>-3.827948541726676</v>
+        <v>-3.979604632880688</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.735799271049228</v>
       </c>
       <c r="E47">
-        <v>-21.53200387380064</v>
+        <v>-22.12450488449022</v>
       </c>
       <c r="F47">
-        <v>7.522731525340154</v>
+        <v>4.824304110906258</v>
       </c>
       <c r="G47">
-        <v>-2.622658363970979</v>
+        <v>-4.866277976300308</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.530790959586271</v>
       </c>
       <c r="E48">
-        <v>-20.83784315011287</v>
+        <v>-19.15097752530764</v>
       </c>
       <c r="F48">
-        <v>7.468263127790445</v>
+        <v>5.061283529268955</v>
       </c>
       <c r="G48">
-        <v>-3.477106857111333</v>
+        <v>-3.830507593428532</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.350170260882269</v>
       </c>
       <c r="E49">
-        <v>-20.69403692952529</v>
+        <v>-21.15987199374632</v>
       </c>
       <c r="F49">
-        <v>7.117858691763975</v>
+        <v>5.088691143841551</v>
       </c>
       <c r="G49">
-        <v>-3.182256429201684</v>
+        <v>-1.931370107733605</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.196054326203089</v>
       </c>
       <c r="E50">
-        <v>-18.55518431401449</v>
+        <v>-19.90921615620395</v>
       </c>
       <c r="F50">
-        <v>7.26134561511462</v>
+        <v>5.115292652103187</v>
       </c>
       <c r="G50">
-        <v>-3.38272982487779</v>
+        <v>-4.54330777458009</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.07324981984606</v>
       </c>
       <c r="E51">
-        <v>-19.57119727084941</v>
+        <v>-20.43086919104353</v>
       </c>
       <c r="F51">
-        <v>6.975147784311895</v>
+        <v>5.378076974652054</v>
       </c>
       <c r="G51">
-        <v>-3.682218327087958</v>
+        <v>-5.153338690556052</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.982924768528019</v>
       </c>
       <c r="E52">
-        <v>-18.70157176478644</v>
+        <v>-17.58628107228135</v>
       </c>
       <c r="F52">
-        <v>7.313519222792856</v>
+        <v>5.27902567187681</v>
       </c>
       <c r="G52">
-        <v>-3.726218787850411</v>
+        <v>-4.187917400393789</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.925476631983075</v>
       </c>
       <c r="E53">
-        <v>-18.26075199098377</v>
+        <v>-17.60309076779782</v>
       </c>
       <c r="F53">
-        <v>7.648965556448002</v>
+        <v>5.22671744919576</v>
       </c>
       <c r="G53">
-        <v>-3.784226166789521</v>
+        <v>-1.281165721638587</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.898801800503328</v>
       </c>
       <c r="E54">
-        <v>-18.25808924826726</v>
+        <v>-17.29423525505268</v>
       </c>
       <c r="F54">
-        <v>7.558140022197549</v>
+        <v>5.0659142853657</v>
       </c>
       <c r="G54">
-        <v>-3.532406209799319</v>
+        <v>-3.123550525153788</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.89797412234291</v>
       </c>
       <c r="E55">
-        <v>-16.67494379213372</v>
+        <v>-17.37832901737512</v>
       </c>
       <c r="F55">
-        <v>7.473782342905752</v>
+        <v>4.811029487923045</v>
       </c>
       <c r="G55">
-        <v>-3.882314320572587</v>
+        <v>-3.249291665826386</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.918905228914533</v>
       </c>
       <c r="E56">
-        <v>-14.84182204230277</v>
+        <v>-16.24595239243909</v>
       </c>
       <c r="F56">
-        <v>7.70247581191887</v>
+        <v>5.1701205508957</v>
       </c>
       <c r="G56">
-        <v>-4.11019241222278</v>
+        <v>-3.135859133468798</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.955912489663993</v>
       </c>
       <c r="E57">
-        <v>-16.71561401719661</v>
+        <v>-14.45576510467486</v>
       </c>
       <c r="F57">
-        <v>7.330718269034529</v>
+        <v>5.384156821661427</v>
       </c>
       <c r="G57">
-        <v>-4.558397241148088</v>
+        <v>-4.484121841428999</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.005648348889694</v>
       </c>
       <c r="E58">
-        <v>-15.23799559086381</v>
+        <v>-17.69676225264648</v>
       </c>
       <c r="F58">
-        <v>7.390207014336181</v>
+        <v>5.052143962430955</v>
       </c>
       <c r="G58">
-        <v>-4.079261985249369</v>
+        <v>-3.284813819462766</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.063695306676043</v>
       </c>
       <c r="E59">
-        <v>-15.5668352594048</v>
+        <v>-15.71621150302182</v>
       </c>
       <c r="F59">
-        <v>7.337067346049526</v>
+        <v>4.594606572342752</v>
       </c>
       <c r="G59">
-        <v>-4.951547697755316</v>
+        <v>-4.196538060978051</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.126388267084167</v>
       </c>
       <c r="E60">
-        <v>-14.8770852694005</v>
+        <v>-15.12932580010174</v>
       </c>
       <c r="F60">
-        <v>7.309032583934417</v>
+        <v>5.343442909987309</v>
       </c>
       <c r="G60">
-        <v>-3.376065696707237</v>
+        <v>-3.839350060563925</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.190175333757672</v>
       </c>
       <c r="E61">
-        <v>-15.15353955062076</v>
+        <v>-14.26140300026565</v>
       </c>
       <c r="F61">
-        <v>7.549220590481794</v>
+        <v>4.619114421384177</v>
       </c>
       <c r="G61">
-        <v>-4.345237834965495</v>
+        <v>-5.344598837996367</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.252847360949282</v>
       </c>
       <c r="E62">
-        <v>-15.09431163907444</v>
+        <v>-13.18697272873177</v>
       </c>
       <c r="F62">
-        <v>7.460056363736638</v>
+        <v>4.93711148326301</v>
       </c>
       <c r="G62">
-        <v>-3.971944030502815</v>
+        <v>-4.023946079833687</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.314524279209186</v>
       </c>
       <c r="E63">
-        <v>-14.7598340203939</v>
+        <v>-15.1990235435538</v>
       </c>
       <c r="F63">
-        <v>7.404514213576261</v>
+        <v>4.674183043475837</v>
       </c>
       <c r="G63">
-        <v>-4.480519967882272</v>
+        <v>-4.529330651313287</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.375007209912754</v>
       </c>
       <c r="E64">
-        <v>-12.64044025769405</v>
+        <v>-11.96148614972404</v>
       </c>
       <c r="F64">
-        <v>7.486320542638286</v>
+        <v>4.359006561832403</v>
       </c>
       <c r="G64">
-        <v>-4.483287583953103</v>
+        <v>-4.495394248990218</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.434414675223982</v>
       </c>
       <c r="E65">
-        <v>-12.03720676360629</v>
+        <v>-13.46579540185805</v>
       </c>
       <c r="F65">
-        <v>7.274499876448259</v>
+        <v>5.285854611784185</v>
       </c>
       <c r="G65">
-        <v>-3.927072896263534</v>
+        <v>-3.690848919308838</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.491500815118271</v>
       </c>
       <c r="E66">
-        <v>-13.05264913271626</v>
+        <v>-14.05109161040142</v>
       </c>
       <c r="F66">
-        <v>6.912716513419357</v>
+        <v>4.700388625258614</v>
       </c>
       <c r="G66">
-        <v>-4.435542896185734</v>
+        <v>-4.341602855963375</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.547098303814606</v>
       </c>
       <c r="E67">
-        <v>-13.107996142038</v>
+        <v>-12.32937937810718</v>
       </c>
       <c r="F67">
-        <v>7.392302257262307</v>
+        <v>4.061607179089775</v>
       </c>
       <c r="G67">
-        <v>-4.089369080780764</v>
+        <v>-5.423648044383084</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.60113851462119</v>
       </c>
       <c r="E68">
-        <v>-11.80073437939976</v>
+        <v>-11.26982967216251</v>
       </c>
       <c r="F68">
-        <v>6.59686695676186</v>
+        <v>4.043673293303339</v>
       </c>
       <c r="G68">
-        <v>-4.327337715234655</v>
+        <v>-4.345823801525946</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.654605554195255</v>
       </c>
       <c r="E69">
-        <v>-12.86171508313085</v>
+        <v>-12.91578959125644</v>
       </c>
       <c r="F69">
-        <v>6.914946371348296</v>
+        <v>4.483620461788755</v>
       </c>
       <c r="G69">
-        <v>-4.533789956154686</v>
+        <v>-5.257875787049619</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.707091995647063</v>
       </c>
       <c r="E70">
-        <v>-12.65405737903512</v>
+        <v>-12.71670881693124</v>
       </c>
       <c r="F70">
-        <v>6.414400279714504</v>
+        <v>3.772246687573918</v>
       </c>
       <c r="G70">
-        <v>-4.040382938436168</v>
+        <v>-4.723795406835616</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.7567521662227</v>
       </c>
       <c r="E71">
-        <v>-12.0857972897086</v>
+        <v>-12.47127458266352</v>
       </c>
       <c r="F71">
-        <v>5.866770611214697</v>
+        <v>4.188602972742949</v>
       </c>
       <c r="G71">
-        <v>-4.182259678067174</v>
+        <v>-5.045179857242523</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.802744934180765</v>
       </c>
       <c r="E72">
-        <v>-12.16121449583234</v>
+        <v>-9.624612422805827</v>
       </c>
       <c r="F72">
-        <v>6.185424911048438</v>
+        <v>4.100824488673802</v>
       </c>
       <c r="G72">
-        <v>-4.736984620264073</v>
+        <v>-6.714949505794586</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.843182453893336</v>
       </c>
       <c r="E73">
-        <v>-13.13443790176879</v>
+        <v>-12.49921979576485</v>
       </c>
       <c r="F73">
-        <v>6.448247242539276</v>
+        <v>3.671288602876484</v>
       </c>
       <c r="G73">
-        <v>-4.000550454507658</v>
+        <v>-5.747005579931397</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.878924147104805</v>
       </c>
       <c r="E74">
-        <v>-12.2662207511222</v>
+        <v>-12.57506720691933</v>
       </c>
       <c r="F74">
-        <v>6.599418306991633</v>
+        <v>4.236346954975701</v>
       </c>
       <c r="G74">
-        <v>-4.469866632336898</v>
+        <v>-5.043226635374354</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.909238254784994</v>
       </c>
       <c r="E75">
-        <v>-10.82685434473219</v>
+        <v>-13.55406894568956</v>
       </c>
       <c r="F75">
-        <v>5.843144886368171</v>
+        <v>4.055597015140682</v>
       </c>
       <c r="G75">
-        <v>-4.102266966201765</v>
+        <v>-3.337332313897764</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.933047729314257</v>
       </c>
       <c r="E76">
-        <v>-11.17439661092486</v>
+        <v>-11.92545761051901</v>
       </c>
       <c r="F76">
-        <v>5.920847833403293</v>
+        <v>4.13616963729458</v>
       </c>
       <c r="G76">
-        <v>-3.563962329879652</v>
+        <v>-4.987579675404744</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.949124705990076</v>
       </c>
       <c r="E77">
-        <v>-13.44030462166887</v>
+        <v>-13.07380616328009</v>
       </c>
       <c r="F77">
-        <v>5.623836458609948</v>
+        <v>4.126496361563075</v>
       </c>
       <c r="G77">
-        <v>-3.740616350400702</v>
+        <v>-3.43487422766685</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.95617543765894</v>
       </c>
       <c r="E78">
-        <v>-13.24889508231266</v>
+        <v>-13.69341009090558</v>
       </c>
       <c r="F78">
-        <v>5.894173474669546</v>
+        <v>3.651656984348697</v>
       </c>
       <c r="G78">
-        <v>-3.471727220610017</v>
+        <v>-3.788655676721066</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.955942571551022</v>
       </c>
       <c r="E79">
-        <v>-12.03916306437761</v>
+        <v>-14.82524329896069</v>
       </c>
       <c r="F79">
-        <v>5.581728885730244</v>
+        <v>3.749146753091318</v>
       </c>
       <c r="G79">
-        <v>-3.305405412717033</v>
+        <v>-2.128711727329561</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.948672902749498</v>
       </c>
       <c r="E80">
-        <v>-14.19965272869706</v>
+        <v>-14.54999812030048</v>
       </c>
       <c r="F80">
-        <v>6.200313330359484</v>
+        <v>2.985444168018531</v>
       </c>
       <c r="G80">
-        <v>-3.282953292869696</v>
+        <v>-4.394124660943913</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.935197405625489</v>
       </c>
       <c r="E81">
-        <v>-16.09714673654705</v>
+        <v>-15.52062218215652</v>
       </c>
       <c r="F81">
-        <v>5.06767536634367</v>
+        <v>3.248355187040633</v>
       </c>
       <c r="G81">
-        <v>-2.154245965073959</v>
+        <v>-4.078785266691714</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.914670995955985</v>
       </c>
       <c r="E82">
-        <v>-14.69374547072596</v>
+        <v>-13.77489092372559</v>
       </c>
       <c r="F82">
-        <v>5.899390201955003</v>
+        <v>3.209453034933779</v>
       </c>
       <c r="G82">
-        <v>-2.861494361356159</v>
+        <v>-2.406380423890392</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.890364280484304</v>
       </c>
       <c r="E83">
-        <v>-15.00841101562294</v>
+        <v>-15.41749524357985</v>
       </c>
       <c r="F83">
-        <v>5.173093166898981</v>
+        <v>3.449336969945392</v>
       </c>
       <c r="G83">
-        <v>-2.43496367407646</v>
+        <v>-3.033493754848994</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.865438555194022</v>
       </c>
       <c r="E84">
-        <v>-16.49888125118951</v>
+        <v>-16.81673031331388</v>
       </c>
       <c r="F84">
-        <v>5.489042497029151</v>
+        <v>3.48396311608056</v>
       </c>
       <c r="G84">
-        <v>-2.39948455753209</v>
+        <v>-2.795637678943438</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.844995202648817</v>
       </c>
       <c r="E85">
-        <v>-16.86070179592836</v>
+        <v>-16.31821325217949</v>
       </c>
       <c r="F85">
-        <v>5.023234994650522</v>
+        <v>3.58957571246347</v>
       </c>
       <c r="G85">
-        <v>-1.93134693391483</v>
+        <v>-5.095066467973801</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.833876615692368</v>
       </c>
       <c r="E86">
-        <v>-17.78383122239196</v>
+        <v>-19.55921040015111</v>
       </c>
       <c r="F86">
-        <v>5.15604615642519</v>
+        <v>3.093597028689806</v>
       </c>
       <c r="G86">
-        <v>-1.199338967544421</v>
+        <v>-2.671184340485616</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.836231957086873</v>
       </c>
       <c r="E87">
-        <v>-18.21893153352294</v>
+        <v>-21.07883495137906</v>
       </c>
       <c r="F87">
-        <v>5.06396632708971</v>
+        <v>3.424802197903404</v>
       </c>
       <c r="G87">
-        <v>-1.815931384779219</v>
+        <v>-2.971291914711628</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.858195594002509</v>
       </c>
       <c r="E88">
-        <v>-20.14810221705658</v>
+        <v>-21.62817507630153</v>
       </c>
       <c r="F88">
-        <v>5.118144906456894</v>
+        <v>2.516306132099734</v>
       </c>
       <c r="G88">
-        <v>-1.211439011490457</v>
+        <v>-1.225730636583491</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.904191097975486</v>
       </c>
       <c r="E89">
-        <v>-21.99666153477968</v>
+        <v>-22.38238336533102</v>
       </c>
       <c r="F89">
-        <v>4.426150941529289</v>
+        <v>2.630432731484047</v>
       </c>
       <c r="G89">
-        <v>-0.7557722129196317</v>
+        <v>-1.325891191874141</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.981228681530001</v>
       </c>
       <c r="E90">
-        <v>-22.38871870046775</v>
+        <v>-24.67084770510724</v>
       </c>
       <c r="F90">
-        <v>4.388561681626333</v>
+        <v>2.610957899841888</v>
       </c>
       <c r="G90">
-        <v>-1.338746040203131</v>
+        <v>-2.096377629047499</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.092695336404992</v>
       </c>
       <c r="E91">
-        <v>-22.5946736983366</v>
+        <v>-24.37896491294284</v>
       </c>
       <c r="F91">
-        <v>4.496872912889152</v>
+        <v>2.393005124347281</v>
       </c>
       <c r="G91">
-        <v>-1.286114987219797</v>
+        <v>-3.589612436717925</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.239178898925611</v>
       </c>
       <c r="E92">
-        <v>-24.12326462809973</v>
+        <v>-26.10743362845653</v>
       </c>
       <c r="F92">
-        <v>4.409886281777726</v>
+        <v>1.561342551031155</v>
       </c>
       <c r="G92">
-        <v>-0.3095669535000433</v>
+        <v>-1.449328192851406</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.419332612999102</v>
       </c>
       <c r="E93">
-        <v>-27.72903488586321</v>
+        <v>-28.11868743185321</v>
       </c>
       <c r="F93">
-        <v>3.603529745284408</v>
+        <v>1.580180732895307</v>
       </c>
       <c r="G93">
-        <v>-1.663186124142786</v>
+        <v>-1.098618930057634</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.627286787012909</v>
       </c>
       <c r="E94">
-        <v>-28.7508080616359</v>
+        <v>-31.00598358898173</v>
       </c>
       <c r="F94">
-        <v>3.566249308034963</v>
+        <v>1.467886481255158</v>
       </c>
       <c r="G94">
-        <v>-0.3967501702767501</v>
+        <v>-1.898016361425448</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.861226366917762</v>
       </c>
       <c r="E95">
-        <v>-29.32170372283488</v>
+        <v>-30.88548542411163</v>
       </c>
       <c r="F95">
-        <v>2.878765737554529</v>
+        <v>1.172371708551903</v>
       </c>
       <c r="G95">
-        <v>-1.419993448827924</v>
+        <v>-1.925133039937618</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.11768396079168</v>
       </c>
       <c r="E96">
-        <v>-33.79497789658874</v>
+        <v>-35.83528865345563</v>
       </c>
       <c r="F96">
-        <v>2.620268506918757</v>
+        <v>0.7809857145516066</v>
       </c>
       <c r="G96">
-        <v>-0.6773553207309151</v>
+        <v>-2.357758441555116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.388835655469432</v>
       </c>
       <c r="E97">
-        <v>-34.38017674294095</v>
+        <v>-35.54068877688664</v>
       </c>
       <c r="F97">
-        <v>2.314899916009638</v>
+        <v>0.8416749089371617</v>
       </c>
       <c r="G97">
-        <v>-0.6014809275163588</v>
+        <v>-2.910682446978651</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.673152971278653</v>
       </c>
       <c r="E98">
-        <v>-36.86053969726621</v>
+        <v>-38.66153192401274</v>
       </c>
       <c r="F98">
-        <v>2.147513286689096</v>
+        <v>0.5947529848373356</v>
       </c>
       <c r="G98">
-        <v>-1.090696794582158</v>
+        <v>-2.504435472218066</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.958684565340043</v>
       </c>
       <c r="E99">
-        <v>-38.97952816154237</v>
+        <v>-40.40288867655227</v>
       </c>
       <c r="F99">
-        <v>1.622323147305151</v>
+        <v>-0.1609265460678357</v>
       </c>
       <c r="G99">
-        <v>-1.384802349745472</v>
+        <v>-2.765803042543526</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.255706773216003</v>
       </c>
       <c r="E100">
-        <v>-40.84960452351292</v>
+        <v>-42.53962649470148</v>
       </c>
       <c r="F100">
-        <v>1.537796011480402</v>
+        <v>-0.4833579845098991</v>
       </c>
       <c r="G100">
-        <v>-0.209191212749341</v>
+        <v>-3.786517064302696</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.543177300987674</v>
       </c>
       <c r="E101">
-        <v>-42.62954840307179</v>
+        <v>-43.34871988870393</v>
       </c>
       <c r="F101">
-        <v>1.305151196208262</v>
+        <v>-0.7674431516214272</v>
       </c>
       <c r="G101">
-        <v>-1.109523867063994</v>
+        <v>-3.426078108169007</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.854111190157095</v>
       </c>
       <c r="E102">
-        <v>-45.03817806487854</v>
+        <v>-43.74143368312311</v>
       </c>
       <c r="F102">
-        <v>1.643272409154584</v>
+        <v>-1.015605117453042</v>
       </c>
       <c r="G102">
-        <v>-1.326189140972675</v>
+        <v>-4.46127245611695</v>
       </c>
     </row>
   </sheetData>
